--- a/output/upload/S00027_2126_상생친구_보장보험_무배당.xlsx
+++ b/output/upload/S00027_2126_상생친구_보장보험_무배당.xlsx
@@ -2611,17 +2611,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">
@@ -2702,17 +2694,9 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="inlineStr">
@@ -2793,17 +2777,9 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="inlineStr">
@@ -2884,17 +2860,9 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="6" t="inlineStr">
@@ -2975,17 +2943,9 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="6" t="inlineStr">
@@ -3066,17 +3026,9 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="inlineStr">
@@ -3157,17 +3109,9 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="6" t="inlineStr">
@@ -3248,17 +3192,9 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
+      <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="6" t="inlineStr">
@@ -3338,16 +3274,8 @@
       <c r="AW14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3391,16 +3319,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3444,16 +3364,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3497,16 +3409,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3550,16 +3454,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3603,16 +3499,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3656,16 +3544,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3709,16 +3589,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3762,16 +3634,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3815,16 +3679,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3868,16 +3724,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3921,16 +3769,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3974,16 +3814,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4027,16 +3859,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4080,16 +3904,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4133,16 +3949,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4186,16 +3994,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4239,16 +4039,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4292,16 +4084,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4345,16 +4129,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4398,16 +4174,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4451,16 +4219,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2126A01</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>6552002</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>20260201</t>

--- a/output/upload/S00027_2126_상생친구_보장보험_무배당.xlsx
+++ b/output/upload/S00027_2126_상생친구_보장보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW36"/>
+  <dimension ref="A1:AW51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>X20</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="N12" s="6" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>X30</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -3140,15 +3140,15 @@
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N13" s="6" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
@@ -3209,12 +3209,12 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
@@ -3223,15 +3223,15 @@
         </is>
       </c>
       <c r="L14" s="6" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N14" s="6" t="n">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -3302,15 +3302,15 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>10</v>
+        <v>999</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>N7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -3441,11 +3441,11 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -3513,12 +3513,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -3558,12 +3558,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X20</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3572,15 +3572,15 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -3603,12 +3603,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X30</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3617,15 +3617,15 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -3648,12 +3648,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3662,15 +3662,15 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -3693,12 +3693,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3707,15 +3707,15 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3748,11 +3748,11 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3793,11 +3793,11 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3838,11 +3838,11 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -3873,21 +3873,21 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
           <t>N20</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3928,11 +3928,11 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -3963,25 +3963,25 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X20</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -4008,29 +4008,29 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>X30</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -4053,29 +4053,29 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>X1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -4098,29 +4098,29 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
           <t>A999</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>999</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N33" t="n">
-        <v>10</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -4143,21 +4143,21 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>999</v>
+        <v>20</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -4188,21 +4188,21 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>N7</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>999</v>
+        <v>20</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -4233,31 +4233,706 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>20</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>10</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>20</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>20</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>N30</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>20</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>30</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>X20</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>20</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>20</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>X30</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>20</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>30</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>20</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>20</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
           <t>A999</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>20</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>999</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>A999</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L36" t="n">
+      <c r="L43" t="n">
         <v>999</v>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>5</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="N36" t="n">
+      <c r="L44" t="n">
         <v>999</v>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>7</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>999</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>10</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>999</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>20</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>N30</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>999</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>30</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>X20</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>999</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>20</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>X30</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>999</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>30</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>999</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>999</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>999</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>999</v>
+      </c>
+      <c r="O51" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>

--- a/output/upload/S00027_2126_상생친구_보장보험_무배당.xlsx
+++ b/output/upload/S00027_2126_상생친구_보장보험_무배당.xlsx
@@ -2611,11 +2611,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2694,11 +2714,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2777,11 +2817,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2860,11 +2920,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2943,11 +3023,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3026,11 +3126,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3109,11 +3229,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3192,11 +3332,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3274,8 +3434,31 @@
       <c r="AW14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3319,8 +3502,31 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3364,8 +3570,31 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3409,8 +3638,31 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3454,8 +3706,31 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3499,8 +3774,31 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3544,8 +3842,31 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3589,8 +3910,31 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3634,8 +3978,31 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3679,8 +4046,31 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3724,8 +4114,31 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3769,8 +4182,31 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3814,8 +4250,31 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3859,8 +4318,31 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3904,8 +4386,31 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3949,8 +4454,31 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3994,8 +4522,31 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4039,8 +4590,31 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4084,8 +4658,31 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4129,8 +4726,31 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4174,8 +4794,31 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4219,8 +4862,31 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4264,8 +4930,31 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4309,8 +4998,31 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4354,8 +5066,31 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4399,8 +5134,31 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4444,8 +5202,31 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4489,8 +5270,31 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4534,8 +5338,31 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4579,8 +5406,31 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4624,8 +5474,31 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4669,8 +5542,31 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4714,8 +5610,31 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4759,8 +5678,31 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4804,8 +5746,31 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4849,8 +5814,31 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4894,8 +5882,31 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2126A04</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>20260201</t>

--- a/output/upload/S00027_2126_상생친구_보장보험_무배당.xlsx
+++ b/output/upload/S00027_2126_상생친구_보장보험_무배당.xlsx
@@ -2623,7 +2623,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>2126004</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">

--- a/output/upload/S00027_2126_상생친구_보장보험_무배당.xlsx
+++ b/output/upload/S00027_2126_상생친구_보장보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW51"/>
+  <dimension ref="A1:AW135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5257,11 +5257,11 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>20</v>
+        <v>999</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -5307,29 +5307,29 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>999</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L42" t="n">
-        <v>20</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
       <c r="N42" t="n">
-        <v>999</v>
+        <v>5</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N7</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -5397,7 +5397,7 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>X20</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5665,11 +5665,11 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>X20</t>
+          <t>X30</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X30</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5801,11 +5801,11 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>30</v>
+        <v>999</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -5816,22 +5816,22 @@
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
-          <t>2126A04</t>
+          <t>2126A05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2126004</t>
+          <t>2126005</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5851,29 +5851,29 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>999</v>
+        <v>5</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -5884,22 +5884,22 @@
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
-          <t>2126A04</t>
+          <t>2126A05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2126004</t>
+          <t>2126005</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5919,31 +5919,5743 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>90</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>7</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>90</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>10</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>90</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>20</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>N30</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>90</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>30</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>X20</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>90</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>20</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>X30</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>90</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>30</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>90</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>90</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
           <t>A999</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>90</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>999</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>100</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>5</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>100</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>7</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>100</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>10</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>100</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>20</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>N30</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>100</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>30</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>X20</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>100</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>20</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>X30</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>100</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>30</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>100</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>100</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
         <is>
           <t>A999</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>100</v>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L51" t="n">
+      <c r="N67" t="n">
         <v>999</v>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>1</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>5</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>1</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>7</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>1</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>10</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>20</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>N30</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>30</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>X20</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>1</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>20</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>X30</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>1</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>30</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>1</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="N51" t="n">
+      <c r="N76" t="n">
         <v>999</v>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>20</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>5</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>20</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>7</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>20</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>10</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>20</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>20</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>N30</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>20</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>30</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>X20</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>20</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>20</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>X30</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>20</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>30</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>20</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>999</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>999</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>5</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>999</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>7</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>999</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>10</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>999</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>20</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>N30</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>999</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>30</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>X20</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>999</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>20</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>X30</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>999</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>30</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2126A05</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2126005</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>999</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>999</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>90</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>5</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>90</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>7</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>90</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>10</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>90</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>20</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>N30</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>90</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>30</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>X20</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>90</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>20</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>X30</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>90</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>30</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>90</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>90</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>90</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>999</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>100</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>5</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>100</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>7</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>100</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>10</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>100</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>20</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>N30</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>100</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>30</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>X20</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>100</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>20</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>X30</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>100</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>30</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>100</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>100</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>100</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>999</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>1</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>5</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>1</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>7</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>1</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>10</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>20</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>N30</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>1</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>30</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>X20</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>1</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>20</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>X30</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>1</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>30</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>1</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>1</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>1</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>999</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>20</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>5</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>20</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>7</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>20</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>10</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>20</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>20</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>N30</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>20</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>30</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>X20</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>20</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>20</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>X30</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>20</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>30</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>20</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>999</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>999</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>5</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>999</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>7</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>999</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>10</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>999</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>20</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>N30</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>999</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>30</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>X20</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>999</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>20</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>X30</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>999</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>30</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2126A06</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2126006</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>999</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>999</v>
+      </c>
+      <c r="O135" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>

--- a/output/upload/S00027_2126_상생친구_보장보험_무배당.xlsx
+++ b/output/upload/S00027_2126_상생친구_보장보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW135"/>
+  <dimension ref="A1:AW132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>X20</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5053,11 +5053,11 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X20</t>
+          <t>X30</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>X30</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5189,11 +5189,11 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>30</v>
+        <v>999</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -5239,29 +5239,29 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>999</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L41" t="n">
-        <v>20</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
       <c r="N41" t="n">
-        <v>999</v>
+        <v>5</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N7</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -5397,7 +5397,7 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>X20</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -5597,11 +5597,11 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>X20</t>
+          <t>X30</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5669,7 +5669,7 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>X30</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5733,11 +5733,11 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>30</v>
+        <v>999</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -5748,22 +5748,22 @@
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>2126A04</t>
+          <t>2126A05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2126004</t>
+          <t>2126005</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 1종(출생아가입형)</t>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5783,29 +5783,29 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>999</v>
+        <v>5</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N7</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>X20</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -6141,11 +6141,11 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>X20</t>
+          <t>X30</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -6213,7 +6213,7 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X30</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -6281,7 +6281,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -6345,11 +6345,11 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>90</v>
+        <v>999</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -6395,12 +6395,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -6409,15 +6409,15 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>999</v>
+        <v>5</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N7</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6621,7 +6621,7 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>X20</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6753,11 +6753,11 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>X20</t>
+          <t>X30</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>X30</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6893,7 +6893,7 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6957,11 +6957,11 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>100</v>
+        <v>999</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X1</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -7021,15 +7021,15 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>999</v>
+        <v>5</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N7</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -7097,7 +7097,7 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>X20</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7365,11 +7365,11 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>X20</t>
+          <t>X30</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7437,7 +7437,7 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>X30</t>
+          <t>X1</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7505,7 +7505,7 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7569,11 +7569,11 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -7619,29 +7619,29 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>999</v>
+        <v>5</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N7</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -7845,7 +7845,7 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X20</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N80" t="n">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>X30</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N81" t="n">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>X20</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -8045,11 +8045,11 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N82" t="n">
-        <v>20</v>
+        <v>999</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -8095,29 +8095,29 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>X30</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>999</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L83" t="n">
-        <v>20</v>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="N83" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -8163,29 +8163,29 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N7</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>999</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L84" t="n">
-        <v>20</v>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
       <c r="N84" t="n">
-        <v>999</v>
+        <v>7</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -8321,7 +8321,7 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -8389,7 +8389,7 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X20</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N88" t="n">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>X30</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N89" t="n">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>X20</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -8589,11 +8589,11 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N90" t="n">
-        <v>20</v>
+        <v>999</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -8604,22 +8604,22 @@
     <row r="91">
       <c r="B91" t="inlineStr">
         <is>
-          <t>2126A05</t>
+          <t>2126A06</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2126005</t>
+          <t>2126006</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -8639,29 +8639,29 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>X30</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N91" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -8672,22 +8672,22 @@
     <row r="92">
       <c r="B92" t="inlineStr">
         <is>
-          <t>2126A05</t>
+          <t>2126A06</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2126005</t>
+          <t>2126006</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 2종(태아가입형 23주 이내)</t>
+          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -8707,29 +8707,29 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N7</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>999</v>
+        <v>90</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N92" t="n">
-        <v>999</v>
+        <v>7</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -8797,7 +8797,7 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X20</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N96" t="n">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>X30</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N97" t="n">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>X20</t>
+          <t>X90</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>X30</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -9201,11 +9201,11 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N99" t="n">
-        <v>30</v>
+        <v>999</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -9251,12 +9251,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -9265,15 +9265,15 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N100" t="n">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
@@ -9319,12 +9319,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>X90</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N7</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -9333,15 +9333,15 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N101" t="n">
-        <v>999</v>
+        <v>7</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -9409,7 +9409,7 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -9477,7 +9477,7 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -9545,7 +9545,7 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X20</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N105" t="n">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>X30</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N106" t="n">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>X20</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -9749,7 +9749,7 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>X30</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -9813,11 +9813,11 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N108" t="n">
-        <v>30</v>
+        <v>999</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X1</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -9877,15 +9877,15 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -9931,12 +9931,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X1</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N7</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -9945,15 +9945,15 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N110" t="n">
-        <v>999</v>
+        <v>7</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -10157,7 +10157,7 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X20</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N114" t="n">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>X30</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N115" t="n">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>X20</t>
+          <t>X1</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -10361,7 +10361,7 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>X30</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -10425,11 +10425,11 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N117" t="n">
-        <v>30</v>
+        <v>999</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -10475,29 +10475,29 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N118" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -10543,29 +10543,29 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>X1</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N7</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N119" t="n">
-        <v>999</v>
+        <v>7</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -10701,7 +10701,7 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X20</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -10765,11 +10765,11 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N122" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X30</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -10833,11 +10833,11 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N123" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -10901,11 +10901,11 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N124" t="n">
-        <v>30</v>
+        <v>999</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -10951,29 +10951,29 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>X20</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>999</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L125" t="n">
-        <v>20</v>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="N125" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -11019,29 +11019,29 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>X30</t>
+          <t>N7</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>999</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L126" t="n">
-        <v>20</v>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="N126" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -11087,29 +11087,29 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>999</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L127" t="n">
-        <v>20</v>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
       <c r="N127" t="n">
-        <v>999</v>
+        <v>10</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -11177,7 +11177,7 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -11245,7 +11245,7 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X20</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -11309,11 +11309,11 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N130" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X30</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -11377,11 +11377,11 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N131" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -11445,217 +11445,13 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N132" t="n">
-        <v>30</v>
+        <v>999</v>
       </c>
       <c r="O132" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>2126A06</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2126006</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>X20</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L133" t="n">
-        <v>999</v>
-      </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N133" t="n">
-        <v>20</v>
-      </c>
-      <c r="O133" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>2126A06</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>2126006</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>X30</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L134" t="n">
-        <v>999</v>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N134" t="n">
-        <v>30</v>
-      </c>
-      <c r="O134" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>2126A06</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>2126006</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>한화생명 상생친구 보장보험 무배당 보장형 계약 3종(태아가입형 23주 초과)</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L135" t="n">
-        <v>999</v>
-      </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N135" t="n">
-        <v>999</v>
-      </c>
-      <c r="O135" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>
